--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -415,7 +415,7 @@
     <t>Monthly B2B Retainer + Per-Trader Seat</t>
   </si>
   <si>
-    <t>Phase 1 Q1-Q2</t>
+    <t>Executed Directly (Live)</t>
   </si>
   <si>
     <t>SAAS-02</t>
@@ -481,7 +481,7 @@
     <t>AUM / Volume-based Basis Point Fee</t>
   </si>
   <si>
-    <t>Phase 2 Q3-Q4</t>
+    <t>Executed Directly (Live)</t>
   </si>
   <si>
     <t>SAAS-05</t>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -55,7 +55,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border/>
     <border>
       <left style="thin">
@@ -85,11 +85,43 @@
         <color rgb="FF747780"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF767680"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF767680"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF767680"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF767680"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF767680"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF767680"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF767680"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF767680"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -108,6 +140,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1679,7 +1713,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Causal rule-based regimes (models/regimes.py) + Hawkes re-export; models/quant/regime.py has a GaussianHMM (hmmlearn, GMM fallback). audit-and-gap.md says 'No HMM' - inconsistent with code. No change-point model. Macro regime tagging not implemented. price_action candidates carry market_regime=None.</t>
+          <t>Causal rule-based regimes (models/regimes.py) + Hawkes re-export; models/quant/regime.py has a GaussianHMM (hmmlearn, GMM fallback). (audit-and-gap.md corrected 2026-10-23.) No change-point model. Macro regime tagging not implemented. price_action candidates carry market_regime=None.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4598,7 +4632,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Driven by whale_saas_az.py constants, which still label items 'Executed Directly (Live)'/'ACTIVE' - see Changelog inconsistencies.</t>
+          <t>Driven by whale_saas_az.py constants (statuses aligned with this workbook 2026-10-23; WF metrics labelled sample inputs). The 100-feature matrix (proctoring_and_features100.py) still says ACTIVE - not yet audited.</t>
         </is>
       </c>
     </row>
@@ -4980,42 +5014,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>SAAS-01</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Real-Time Risk &amp; Drawdown Engine</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Prop Firm Founder, Head of Risk</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Delayed equity updates lead to catastrophic firm losses when traders breach max drawdown during volatile events.</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Deterministic multi-broker margin &amp; equity monitoring, millisecond kill-switch using ATLAS Control Plane.</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>US Equities, CME Futures, FX/CFDs, 24/7 Crypto</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Monthly B2B Retainer + Per-Trader Seat</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5027,47 +5061,47 @@
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>Building blocks exist (paper): control plane, rulebooks, one Safe stop. No multi-broker margin feed, no customers. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py still hard-codes phase 'Executed Directly (Live)'/status 'ACTIVE' with illustrative telemetry - overclaim in code.</t>
+          <t>Building blocks exist (paper): control plane, rulebooks, one Safe stop. No multi-broker margin feed, no customers. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py now reports phase/status 'Planned' with no invented telemetry (fixed 2026-10-23 on atlas-docs-1).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>SAAS-02</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Trader Evaluation &amp; Challenge Lifecycle Engine</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Prop Firm Founder, Operations Lead</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Manual challenge verification and easily gamified rules lead to unprofitable funded traders.</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Configurable pass/fail criteria, consistency scorecards, anti-gaming algorithms powered by ATLAS walk-forward validation.</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>FX/CFDs, CME Futures</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Revenue Share on Evaluation Fees</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5079,47 +5113,47 @@
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>Building blocks exist: competition rulebook (consistency 35%, min 5 days), walk-forward. No challenge lifecycle product. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py still hard-codes phase 'Executed Directly (Live)'/status 'ACTIVE' with illustrative telemetry - overclaim in code.</t>
+          <t>Building blocks exist: competition rulebook (consistency 35%, min 5 days), walk-forward. No challenge lifecycle product. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py now reports phase/status 'Planned' with no invented telemetry (fixed 2026-10-23 on atlas-docs-1).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>SAAS-03</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Sybil &amp; Latency Arbitrage Detection</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Head of Risk, Compliance Officer</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Sophisticated rings use account sharing and toxic tick-scalping to extract risk-free profits from B-Book firms.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Account-sharing detection, toxic tick-scalping identifier, IP/behavioral fingerprinting using ATLAS ML models.</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>FX/CFDs, 24/7 Crypto</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Tiered SaaS Subscription based on Trade Volume</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5131,47 +5165,47 @@
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>No account-sharing / latency-arbitrage detector found in src. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py still hard-codes phase 'Executed Directly (Live)'/status 'ACTIVE' with illustrative telemetry - overclaim in code.</t>
+          <t>No account-sharing / latency-arbitrage detector found in src. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py now reports phase/status 'Planned' with no invented telemetry (fixed 2026-10-23 on atlas-docs-1).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>SAAS-04</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>AI-Powered Synthetic Copier / Dealing Desk Hedger</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Dealing Desk Lead, Chief Investment Officer</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Inefficient manual B-Book to A-Book routing leaves alpha on the table and exposes the firm to directional risk.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>B-Book to A-Book smart order routing, alpha clustering utilizing ATLAS regime classification engine.</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>US Equities, FX/CFDs, 24/7 Crypto</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>AUM / Volume-based Basis Point Fee</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5183,47 +5217,47 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>No B-Book/A-Book router; regime classification is rule-based (models/regimes.py). Live routing disabled. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py still hard-codes phase 'Executed Directly (Live)'/status 'ACTIVE' with illustrative telemetry - overclaim in code.</t>
+          <t>No B-Book/A-Book router; regime classification is rule-based (models/regimes.py). Live routing disabled. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py now reports phase/status 'Planned' with no invented telemetry (fixed 2026-10-23 on atlas-docs-1).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>SAAS-05</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Point-in-Time Regulatory &amp; Audit Ledger</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Compliance Officer, Legal Counsel</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Increasing regulatory scrutiny requires immutable, point-in-time proof of trade execution and pricing.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>ISO 42001 &amp; IOSCO aligned tamper-proof trade audit logs backed by ATLAS Journaling &amp; Immutable Audit Trails.</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Global (All Asset Classes)</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Fixed Enterprise Annual License</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5235,47 +5269,47 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>Building blocks exist: hash-chained audit (governance/audit). Not packaged or licensed. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py still hard-codes phase 'Executed Directly (Live)'/status 'ACTIVE' with illustrative telemetry - overclaim in code.</t>
+          <t>Building blocks exist: hash-chained audit (governance/audit). Not packaged or licensed. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py now reports phase/status 'Planned' with no invented telemetry (fixed 2026-10-23 on atlas-docs-1).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>SAAS-06</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Prop Trader Behavioral Co-Pilot &amp; Coach</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Prop Trader, Community Manager</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>High churn rate of funded traders due to emotional trading and lack of personalized, data-driven feedback.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Execution bias detection, overtrading alerts, disciplined sizing guides leveraging ATLAS Probability Calibration.</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>US Equities, CME Futures, FX/CFDs</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>B2B2C Freemium Upsell</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5287,47 +5321,47 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>No behavioural co-pilot product; calibration exists in predict(). Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py still hard-codes phase 'Executed Directly (Live)'/status 'ACTIVE' with illustrative telemetry - overclaim in code.</t>
+          <t>No behavioural co-pilot product; calibration exists in predict(). Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py now reports phase/status 'Planned' with no invented telemetry (fixed 2026-10-23 on atlas-docs-1).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>SAAS-07</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Multi-Broker Bridge &amp; Execution Router</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>CTO, Head of Trading</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Fragmented API integrations across different asset classes create a maintenance nightmare and execution latency.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Unified FIX / REST abstraction across Alpaca, IBKR, cTrader, DXtrade, Bybit via ATLAS Execution Routing.</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Global (All Asset Classes)</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Monthly B2B Retainer + API Call Volume Tier</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5339,47 +5373,47 @@
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>Only paper adapters (Alpaca/IBKR paper, paper broker). No cTrader/DXtrade/Bybit/FIX. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py still hard-codes phase 'Executed Directly (Live)'/status 'ACTIVE' with illustrative telemetry - overclaim in code.</t>
+          <t>Only paper adapters (Alpaca/IBKR paper, paper broker). No cTrader/DXtrade/Bybit/FIX. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py now reports phase/status 'Planned' with no invented telemetry (fixed 2026-10-23 on atlas-docs-1).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>SAAS-08</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Dynamic Margin &amp; Trailing Drawdown Visualizer</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Prop Trader, Frontend Developer</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Traders lack real-time visibility into their complex trailing drawdown limits, causing accidental breaches and support tickets.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Interactive real-time remaining-room HUD for web &amp; mobile streaming from ATLAS Data Lakehouse.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>US Equities, CME Futures, FX/CFDs, 24/7 Crypto</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Flat Monthly API Access Fee</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5391,47 +5425,47 @@
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>Remaining-room HUD exists in UI on paper data (Overview/Account risk). Not a product. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py still hard-codes phase 'Executed Directly (Live)'/status 'ACTIVE' with illustrative telemetry - overclaim in code.</t>
+          <t>Remaining-room HUD exists in UI on paper data (Overview/Account risk). Not a product. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py now reports phase/status 'Planned' with no invented telemetry (fixed 2026-10-23 on atlas-docs-1).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>SAAS-09</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Backtesting &amp; Rule Verification Sandbox</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Quant Researcher, Prop Trader</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Traders cannot accurately backtest their strategies against the specific, complex rules of prop firm evaluations.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Deterministic prop evaluation replay for strategy verification using ATLAS Zero Data-Leakage Research Sandbox.</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>US Equities, CME Futures, FX/CFDs</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Pay-per-Compute / Backtest Hour</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5443,47 +5477,47 @@
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>Building blocks exist: deterministic replay harness + setup evidence. Not a product. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py still hard-codes phase 'Executed Directly (Live)'/status 'ACTIVE' with illustrative telemetry - overclaim in code.</t>
+          <t>Building blocks exist: deterministic replay harness + setup evidence. Not a product. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py now reports phase/status 'Planned' with no invented telemetry (fixed 2026-10-23 on atlas-docs-1).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>SAAS-10</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Whale &amp; Microstructure Liquidity Intelligence</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Dealing Desk Lead, Head of Risk</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Prop firms unknowingly internalize toxic, informed institutional flow, resulting in severe B-Book losses.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Institutional flow detector protecting firm B-Book from toxic informed flow powered by ATLAS Feature Engineering.</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>US Equities, 24/7 Crypto</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Premium Data Feed Subscription</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -5495,7 +5529,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Formula modules only (VPIN/OFI/Kyle λ); no institutional flow data. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py still hard-codes phase 'Executed Directly (Live)'/status 'ACTIVE' with illustrative telemetry - overclaim in code.</t>
+          <t>Formula modules only (VPIN/OFI/Kyle λ); no institutional flow data. Nothing is live or commercialised; ATLAS is paper/simulation only. src/atlas/whale_saas_az.py now reports phase/status 'Planned' with no invented telemetry (fixed 2026-10-23 on atlas-docs-1).</t>
         </is>
       </c>
     </row>
@@ -5581,42 +5615,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>WF-01</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Kyle's Lambda (Price Impact of Informed Trading)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Delta P = lambda * Q + eta</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>P: Price, lambda: Liquidity parameter, Q: Order flow / Quantity, eta: Noise</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>OLS Regression / Rolling Window Estimation</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Lambda spikes indicating high price impact; pause passive market making.</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Widen spreads, skew quotes away from informed flow.</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>src/atlas/liquidity/impact.py</t>
         </is>
@@ -5628,47 +5662,47 @@
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>liquidity/impact.py OLS λ; duplicated in features/microstructure.py and whale_saas_az.py (audit-and-gap: implemented+tested light, duplicated). Not wired to quote widening (no market making). Live demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs.</t>
+          <t>liquidity/impact.py OLS λ; duplicated in features/microstructure.py and whale_saas_az.py (audit-and-gap: implemented+tested light, duplicated). Not wired to quote widening (no market making). Demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs and now says so (input_source: sample_inputs).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>WF-02</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>VPIN (Volume-Synchronized Probability of Informed Trading)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>VPIN = sum(|V_tau^B - V_tau^S|) / (N * V)</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>V_tau^B: Buy volume, V_tau^S: Sell volume, N: Number of buckets, V: Volume per bucket</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Volume-bucketed classification model</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>VPIN &gt; 95th percentile threshold; impending volatility/toxicity.</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Auto-flatten inventory, route orders to A-Book.</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>src/atlas/features/toxicity.py</t>
         </is>
@@ -5680,47 +5714,47 @@
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>features/toxicity.py; control/engine.py VPIN stop-widening / pause thresholds. Duplicated copies. Bars are not true volume-bucketed trade data (no tick feed). Live demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs.</t>
+          <t>features/toxicity.py; control/engine.py VPIN stop-widening / pause thresholds. Duplicated copies. Bars are not true volume-bucketed trade data (no tick feed). Demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs and now says so (input_source: sample_inputs).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>WF-03</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Order Flow Imbalance (OFI) &amp; Multi-Level Depth Imbalance</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>OFI_t = sum_i(Delta L_i,t * w_i)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>L_i,t: Limit order volume at level i, w_i: Weight decay per level</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Exponentially weighted moving average (EWMA) / Vectorized aggregation</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Extreme OFI skew (e.g., &gt; 0.8) at top 3 levels; imminent micro-trend.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Execute aggressive taker orders in direction of imbalance.</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>src/atlas/microstructure/orderbook.py</t>
         </is>
@@ -5732,47 +5766,47 @@
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>marketdata/microstructure.compute_multilevel_ofi + microstructure/orderbook.py entropy. No L2 feed, so not run on real depth. Explicit OBI missing. Live demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs.</t>
+          <t>marketdata/microstructure.compute_multilevel_ofi + microstructure/orderbook.py entropy. No L2 feed, so not run on real depth. Explicit OBI missing. Demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs and now says so (input_source: sample_inputs).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>WF-04</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Almgren-Chriss Optimal Execution Schedule</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>min E[x] + lambda * Var[x] -&gt; x_j = X * sinh(kappa*(T - t_j)) / sinh(kappa*T)</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>X: Total shares, T: Time horizon, kappa: Urgency/risk aversion, lambda: Risk penalty</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Convex Optimization / Dynamic Programming</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Need to liquidate large inventory (Whale flow) over time T.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Slice into TWAP/VWAP child orders following the sinh curve.</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>src/atlas/execution/tactics/optimal.py</t>
         </is>
@@ -5784,47 +5818,47 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>execution/tactics/optimal.py + execution/scheduling.almgren_chriss. Research/paper only; no live slicing. Live demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs.</t>
+          <t>execution/tactics/optimal.py + execution/scheduling.almgren_chriss. Research/paper only; no live slicing. Demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs and now says so (input_source: sample_inputs).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>WF-05</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>GBDT Depth Imbalance &amp; Microstructure Spread Predictor</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>y_hat = sum_m f_m(OFI, VPIN, BookEntropy, SpreadRatio)</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>f_m: Decision trees, BookEntropy: Shannon entropy of depth, SpreadRatio: L1 vs L2 spread</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>LightGBM / XGBoost with early stopping</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>y_hat predicts short-term spread widening or mid-price jump.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Cancel passive resting orders before adverse selection occurs.</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>src/atlas/models/microstructure_gbdt.py</t>
         </is>
@@ -5836,47 +5870,47 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>models/microstructure_gbdt.py uses 4 hand-set threshold 'trees' (fixed constants), not a trained LightGBM/XGBoost model. No validation. Live demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs.</t>
+          <t>models/microstructure_gbdt.py uses 4 hand-set threshold 'trees' (fixed constants), not a trained LightGBM/XGBoost model. No validation. Demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs and now says so (input_source: sample_inputs).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>WF-06</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Cross-Impact &amp; Predatory Liquidation Trigger</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Delta P_predatory = gamma * Sqrt(Volume_whale / ADV) * sgn(Side)</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>gamma: Cross-impact coefficient, ADV: Average Daily Volume</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Square-root impact model calibrated via Non-linear Least Squares</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Detection of large whale liquidation (Volume_whale &gt; 5% ADV).</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Front-run liquidation with momentum shorts, close after impact.</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>src/atlas/microstructure/predatory.py</t>
         </is>
@@ -5888,47 +5922,47 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>microstructure/predatory.py square-root formula with default gamma=0.35; not calibrated by NLS on data. 'Front-run liquidation' action is not implemented and nothing bypasses the control plane. Live demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs.</t>
+          <t>microstructure/predatory.py square-root formula with default gamma=0.35; not calibrated by NLS on data. 'Front-run liquidation' action is not implemented and nothing bypasses the control plane. Demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs and now says so (input_source: sample_inputs).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>WF-07</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Regime-Conditioned Hidden Liquidity Detector (Hawkes Process)</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>lambda(t) = mu_0 + sum_{t_i &lt; t} alpha * exp(-beta*(t - t_i))</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>mu_0: Baseline intensity, alpha: Excitation jump, beta: Decay rate</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Maximum Likelihood Estimation (MLE) of Point Processes</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Clustering of iceberg order fills or hidden prints.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Join the hidden liquidity pool, deploy stealth orders.</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>src/atlas/regime/hawkes_detector.py</t>
         </is>
@@ -5940,47 +5974,47 @@
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>regime/hawkes_detector.py re-exports marketdata.microstructure.compute_hawkes_intensity (intensity only); no MLE fitting of mu/alpha/beta found. Live demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs.</t>
+          <t>regime/hawkes_detector.py re-exports marketdata.microstructure.compute_hawkes_intensity (intensity only); no MLE fitting of mu/alpha/beta found. Demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs and now says so (input_source: sample_inputs).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>WF-08</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Reinforcement Learning Execution Agent (PPO/DDPG)</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>pi*(a|s) maximizing cumulative reward R = -Slippage - Penalty(Inventory)</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>a: Order size/price, s: State (OFI, Spread, Inventory), R: Reward function</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Proximal Policy Optimization (PPO) Deep Neural Network</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Continuous state-action mapping for optimal routing.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Dynamic placement of limit vs market orders based on policy.</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>src/atlas/execution/rl_agent.py</t>
         </is>
@@ -5992,7 +6026,7 @@
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>execution/rl_agent.py is a deterministic rule surrogate; no PPO/DDPG training. Advisory only (execution_permission none). Live demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs.</t>
+          <t>execution/rl_agent.py is a deterministic rule surrogate; no PPO/DDPG training. Advisory only (execution_permission none). Demo /api/master-roadmap/evaluate-whale uses hard-coded sample inputs and now says so (input_source: sample_inputs).</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -6634,6 +6668,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -6718,6 +6753,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -10191,6 +10227,7 @@
         </is>
       </c>
     </row>
+    <row r="151"/>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
@@ -10206,9 +10243,13 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>whale_saas_az.py hard-codes SAAS-01..12 phase 'Executed Directly (Live)', status 'ACTIVE' and illustrative telemetry (e.g. 'Best DSR=0.995', '250 Seats'); nothing is live. Code not changed (docs-only task).</t>
-        </is>
-      </c>
+          <t>FIXED on atlas-docs-1: phases/statuses Planned, telemetry 'Not measured', challenger metrics None. whale_saas_az.py hard-codes SAAS-01..12 phase 'Executed Directly (Live)', status 'ACTIVE' and illustrative telemetry (e.g. 'Best DSR=0.995', '250 Seats'); nothing is live. Code not changed (docs-only task).</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="n"/>
+      <c r="D153" s="10" t="n"/>
+      <c r="E153" s="10" t="n"/>
+      <c r="F153" s="11" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -10221,6 +10262,10 @@
           <t>whale_saas_az.py defines SAAS-11 and SAAS-12; the sheet lists only SAAS-01..10.</t>
         </is>
       </c>
+      <c r="C154" s="10" t="n"/>
+      <c r="D154" s="10" t="n"/>
+      <c r="E154" s="10" t="n"/>
+      <c r="F154" s="11" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -10230,9 +10275,13 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/tab*.csv are exported from whale_saas_az.py constants and repeat the 'Implemented' / 'Live' labels.</t>
-        </is>
-      </c>
+          <t>FIXED: tab1-8 regenerated from corrected constants (tab9 100-feature matrix not audited). docs/roadmap/tab*.csv are exported from whale_saas_az.py constants and repeat the 'Implemented' / 'Live' labels.</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="n"/>
+      <c r="D155" s="10" t="n"/>
+      <c r="E155" s="10" t="n"/>
+      <c r="F155" s="11" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -10245,6 +10294,10 @@
           <t>Track Rules C4 was a date (2026-07-24) produced by '24/7' being parsed with the d/m format; restored to text.</t>
         </is>
       </c>
+      <c r="C156" s="10" t="n"/>
+      <c r="D156" s="10" t="n"/>
+      <c r="E156" s="10" t="n"/>
+      <c r="F156" s="11" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -10257,6 +10310,10 @@
           <t>Track Rules said open-market Max Daily Loss / DD / per-trade cap 'N/A'; code has 3% daily, 10% static DD, 0.50% per-trade (control/engine.py open_rulebook).</t>
         </is>
       </c>
+      <c r="C157" s="10" t="n"/>
+      <c r="D157" s="10" t="n"/>
+      <c r="E157" s="10" t="n"/>
+      <c r="F157" s="11" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -10266,9 +10323,13 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>docs/spec/audit-and-gap.md says 'No HMM' for regimes; models/quant/regime.py fits a GaussianHMM (hmmlearn).</t>
-        </is>
-      </c>
+          <t>FIXED: audit-and-gap corrected. docs/spec/audit-and-gap.md says 'No HMM' for regimes; models/quant/regime.py fits a GaussianHMM (hmmlearn).</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="n"/>
+      <c r="D158" s="10" t="n"/>
+      <c r="E158" s="10" t="n"/>
+      <c r="F158" s="11" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -10281,6 +10342,10 @@
           <t>Sheet 6 paths src/atlas/marketdata/{equities,futures,crypto,fx,synthetics} were directories; they are single .py files.</t>
         </is>
       </c>
+      <c r="C159" s="10" t="n"/>
+      <c r="D159" s="10" t="n"/>
+      <c r="E159" s="10" t="n"/>
+      <c r="F159" s="11" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -10293,6 +10358,10 @@
           <t>Several A-Z paths (market, experiments, fundamentals, integrations, journal, keys) are thin re-export shims; the real code lives elsewhere (paths corrected).</t>
         </is>
       </c>
+      <c r="C160" s="10" t="n"/>
+      <c r="D160" s="10" t="n"/>
+      <c r="E160" s="10" t="n"/>
+      <c r="F160" s="11" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -10302,19 +10371,91 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Test count in README (90 passed) and audit-and-gap baseline (1308) are stale; main is 1404 passed, 9 skipped.</t>
-        </is>
-      </c>
+          <t>FIXED: README, audit-and-gap and broken-code-audit carry the current count. Test count in README (90 passed) and audit-and-gap baseline (1308) are stale; main is 1404 passed, 9 skipped.</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="n"/>
+      <c r="D161" s="10" t="n"/>
+      <c r="E161" s="10" t="n"/>
+      <c r="F161" s="11" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>FIXED: scripts/fetch_public_history.py --15m fills var/evidence_cache_15m (selector evidence cache).</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="n"/>
+      <c r="D162" s="10" t="n"/>
+      <c r="E162" s="10" t="n"/>
+      <c r="F162" s="11" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>FIXED: tests/conftest.py creates the .test-runs/ parent of --basetemp, so fresh worktrees run pytest.</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="n"/>
+      <c r="D163" s="10" t="n"/>
+      <c r="E163" s="10" t="n"/>
+      <c r="F163" s="11" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>OPEN: src/atlas/proctoring_and_features100.py (tab9, 100-feature matrix) still labels every feature ACTIVE with illustrative telemetry (e.g. '0.8ms Tick Equity Check').</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="n"/>
+      <c r="D164" s="10" t="n"/>
+      <c r="E164" s="10" t="n"/>
+      <c r="F164" s="11" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>OPEN: docs/ATLAS_MASTER_ROADMAP.csv is hand-maintained and still says 'Implemented' for most rows.</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="n"/>
+      <c r="D165" s="10" t="n"/>
+      <c r="E165" s="10" t="n"/>
+      <c r="F165" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="13">
     <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B162:F162"/>
     <mergeCell ref="B161:F161"/>
     <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B165:F165"/>
     <mergeCell ref="B159:F159"/>
     <mergeCell ref="B154:F154"/>
     <mergeCell ref="B155:F155"/>
     <mergeCell ref="B160:F160"/>
+    <mergeCell ref="B163:F163"/>
     <mergeCell ref="B157:F157"/>
     <mergeCell ref="B153:F153"/>
   </mergeCells>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>OPEN: src/atlas/proctoring_and_features100.py (tab9, 100-feature matrix) still labels every feature ACTIVE with illustrative telemetry (e.g. '0.8ms Tick Equity Check').</t>
+          <t>FIXED (atlas-docs-1): src/atlas/proctoring_and_features100.py now gives each of the 100 features a verified status (32 Implemented, 36 Partial, 32 Planned) with an evidence note; telemetry reads 'Not measured'. tab9 regenerated.</t>
         </is>
       </c>
       <c r="C164" s="10" t="n"/>
@@ -10435,7 +10435,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>OPEN: docs/ATLAS_MASTER_ROADMAP.csv is hand-maintained and still says 'Implemented' for most rows.</t>
+          <t>FIXED (atlas-docs-1): docs/ATLAS_MASTER_ROADMAP.csv statuses reconciled with code (2 Implemented, 9 Partial, 1 Experimental, 1 Planned, 1 Retired).</t>
         </is>
       </c>
       <c r="C165" s="10" t="n"/>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -345,7 +345,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_3" displayName="Table_3" ref="A1:G30" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_3" displayName="Table_3" ref="A1:G32" headerRowCount="1">
   <tableColumns count="7">
     <tableColumn id="1" name="Layer / Component"/>
     <tableColumn id="2" name="Route / Endpoint"/>
@@ -885,12 +885,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>src/atlas/warehouse</t>
+          <t>src/atlas/warehouse; src/atlas/feeds (authoritative ATLAS feed)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>DuckDB, BigQuery, Parquet ZSTD, acceptance_time &lt;= as_of</t>
+          <t>DuckDB, BigQuery, Parquet ZSTD, acceptance_time &lt;= as_of | ATLAS feed (2026-10-23): one PIT bar store (var/feeds/atlas_feed.sqlite) read by UDF charts, training, evidence and replay; 20 provider adapters with capability manifests (docs/data-feeds.md, docs/data-providers/); quality flags make predict() abstain.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -900,27 +900,27 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>Implemented (paper): keyless Binance/OKX/Kraken/Coinbase/Yahoo live; keyed adapters fixture-tested until env keys set</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>PIT Check; tests/feeds (no network)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>warehouse/__init__.py is a 50-line PIT filter (available_at &lt;= as_of) with a report model. DuckDB is used in features/feature_store.py and api/udf.py. BigQuery, Parquet ZSTD lakehouse, ClickHouse and Databento/Polygon nodes are not wired (named in strings only). Test: tests/test_institutional_expansion.py. | Merged on main (2026-10-23): src/atlas/feeds is the authoritative PIT bar store; udf_feed_bars() (UDF charts + price-action detectors) reads it, falling back to the labelled legacy projection when no series is stored. Yahoo 1h: synthetic 16:00 zero-volume bar dropped, :30-offset bars normalised forward or flagged off_grid_bar (abstain). Tests: tests/feeds, tests/test_udf_spec_parity.py. BigQuery/Parquet/ClickHouse still not wired.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>Partial</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>PIT Check</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>warehouse/__init__.py is a 50-line PIT filter (available_at &lt;= as_of) with a report model. DuckDB is used in features/feature_store.py and api/udf.py. BigQuery, Parquet ZSTD lakehouse, ClickHouse and Databento/Polygon nodes are not wired (named in strings only). Test: tests/test_institutional_expansion.py.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Implemented</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -3612,27 +3612,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Public Yahoo chart bars (SEC EDGAR as-filed selector; Databento/Polygon NOT configured)</t>
+          <t>ATLAS feed: Alpaca IEX / Polygon(Massive) / Tiingo / Databento (keyed) with Yahoo fallback; SEC EDGAR PIT XBRL</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Public Binance/Coinbase klines (Databento NOT configured)</t>
+          <t>ATLAS feed: Binance (data-api.binance.vision) primary, OKX/Bybit/Kraken failover, Coinbase/Kraken/OKX cross-check</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>acceptance_time &lt;= as_of</t>
+          <t>acceptance_time &lt;= as_of; feed receipt_time &lt;= as_of; data_quality flags -&gt; abstain</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Same public bars; feed layer in progress (atlas-feeds-1)</t>
+          <t>Same ATLAS feed store (merged on main); keyed providers off until env keys are set</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Verified: scripts/fetch_public_history.py, marketdata/public_*.py; docs/architecture/CURRENT_STATE.md says Polygon/Databento are not configured.</t>
+          <t>Verified on main 2026-10-23: src/atlas/feeds + tests/feeds; docs/data-feeds.md. Keyed adapters (Polygon/Databento/Alpaca/Tiingo) are fixture-tested only; no keys configured on this box.</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="23.5" customWidth="1" style="7" min="1" max="1"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Databento / Polygon.io</t>
+          <t>atlas.feeds (one PIT store): udf.history / symbol_info; providers per docs/data-feeds.md</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Desk chart on public Yahoo/Binance/Coinbase bars; Databento/Polygon not configured. TradingView/Lightweight Charts rework in progress on atlas-tv-1.</t>
+          <t>Desk chart reads the ATLAS feed via udf_feed_bars() (legacy projection fallback, labelled). TradingView widgets + Lightweight Charts merged from atlas-tv-1 (2026-10-23). Databento/Polygon not configured.</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" s="7">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Curtain Navigation</t>
@@ -4929,6 +4929,80 @@
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>060e8e4 on atlas-ux-2; not merged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" s="7">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TradingView widgets (display only)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>/listings, /market, chart companions</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>TradingView iframe widgets labelled "TradingView display — not ATLAS data". US stocks delayed; no data export (widget-docs/faq/data). Times in America/Toronto.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>src/atlas/marketdata/tradingview.py -&gt; TvFrame.tsx; docs/tradingview-integration.md</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>/listings, /trade (companions)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Implemented+tested</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Merged from atlas-tv-1 on 2026-10-23. Display only: never feeds ATLAS models or orders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" s="7">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ATLAS UDF datafeed + Lightweight Charts</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>/api/udf/* ; /research/price-action</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>UDF-spec: config/symbols/search/history(countback,nextTime)/marks(table)/timescale_marks/time. Bars are the same ones the detectors use. Lightweight Charts (Apache-2.0) with attribution, freshness and stale flags.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>udf_feed_bars() seam -&gt; authoritative ATLAS feed (atlas.feeds); labelled legacy projection fallback</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>/research/price-action, /trade</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Implemented+tested</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Merged on main 2026-10-23. UDF == detector parity: tests/test_udf_spec_parity.py (incl. feed-backed case), tests/test_tradingview_udf.py.</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:F166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -6668,7 +6742,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -6753,7 +6826,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -10227,7 +10299,6 @@
         </is>
       </c>
     </row>
-    <row r="151"/>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
@@ -10442,14 +10513,26 @@
       <c r="D165" s="10" t="n"/>
       <c r="E165" s="10" t="n"/>
       <c r="F165" s="11" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>INTEGRATED (main, 2026-10-23): merged atlas-docs-1, atlas-feeds-1, atlas-tv-1. udf_feed_bars() reads the ATLAS feed (labelled legacy fallback); Yahoo 1h synthetic 16:00 bar dropped, :30 offsets normalised forward or flagged off_grid_bar; Safe stop release is CLI-only (atlas-owner reset, step-up); HTTP release returns 403.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B158:F158"/>
     <mergeCell ref="B162:F162"/>
     <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B164:F164"/>
     <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B164:F164"/>
     <mergeCell ref="B165:F165"/>
     <mergeCell ref="B159:F159"/>
     <mergeCell ref="B154:F154"/>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Single route registry (Home/Trade/Money/Research/Compliance/Settings), aliases for old URLs, PAPER badge, Safe stop pill, Okabe-Ito tokens, shared primitives.</t>
+          <t>Single route registry (pagesMap.ts + nav.ts) drives header, curtain, breadcrumbs, Cmd-K and 404. Branch atlas-ux-3: 11 hub destinations (Overview, Action needed, Trading desk, Risk &amp; positions, Autopilot, Market research, Models &amp; testing, Money, Compliance, Settings, Help &amp; docs) + Advanced (Data tools); merged pages become ?tab= tabs; 39 old URLs 307 to their tab.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Implemented+tested</t>
+          <t>Implemented+tested (hub IA on branch atlas-ux-3, not merged)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Commits a85424e, 23f4dd7, b0b7082. docs/reshape-decisions.md, docs/ux-audit.md.</t>
+          <t>Commits a85424e, 23f4dd7, b0b7082. docs/reshape-decisions.md, docs/ux-audit.md. | atlas-ux-3 @ 2daf292: docs/ux-consolidation.md; test:routes 4/4, page crawl 52 routes + 16 tab URLs 200, interaction crawl 0 failures, layout probe 0 issues (390/768/1440), 39/39 redirects.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Accessible curtain nav replacing the sidebar</t>
+          <t>Header (5 sections + Menu curtain of all hubs, PAPER, Safe stop, account) over hub pages with tabs</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4918,17 +4918,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>branch atlas-ux-2</t>
+          <t>/ /inbox /trade /control /autopilot /research /research/evidence /money /compliance /settings /docs; Advanced /data</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>In progress (branch atlas-ux-2)</t>
+          <t>Implemented+tested (branch atlas-ux-3)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>060e8e4 on atlas-ux-2; not merged.</t>
+          <t>atlas-ux-3 @ 2daf292; not merged. Old routes redirect to hub tabs (see docs/ux-consolidation.md).</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -10514,7 +10514,7 @@
       <c r="E165" s="10" t="n"/>
       <c r="F165" s="11" t="n"/>
     </row>
-    <row r="166">
+    <row r="166" s="7">
       <c r="A166" s="2" t="inlineStr">
         <is>
           <t>•</t>
@@ -10523,6 +10523,50 @@
       <c r="B166" s="2" t="inlineStr">
         <is>
           <t>INTEGRATED (main, 2026-10-23): merged atlas-docs-1, atlas-feeds-1, atlas-tv-1. udf_feed_bars() reads the ATLAS feed (labelled legacy fallback); Yahoo 1h synthetic 16:00 bar dropped, :30 offsets normalised forward or flagged off_grid_bar; Safe stop release is CLI-only (atlas-owner reset, step-up); HTTP release returns 403.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" s="7">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Platform Roadmap (A-Z)</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>NC-16</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>row updated</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Hub IA: 11 destinations + Advanced, tabs, redirects (branch atlas-ux-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" s="7">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>14 Workbench Layers &amp; APIs</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Curtain Navigation</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>row updated</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Implemented+tested (branch atlas-ux-3)</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Research model stack: challengers, GBDT/ridge/stumps, models/quant (triple-barrier, purged WF, CPCV/PBO/DSR, conformal, HMM regime), transformer challengers. NEW unified predict() contract (models/predict.py) - see NC-02. DEFAULT_REGISTRY is EMPTY: no model is validated for trading; every live candidate abstains (no_validated_model). 'perfect-trader' endpoints retired (410 Gone).</t>
+          <t>Research model stack: challengers, GBDT/ridge/stumps, models/quant (triple-barrier, purged WF, CPCV/PBO/DSR, conformal, HMM regime), transformer challengers. NEW unified predict() contract (models/predict.py) - see NC-02. DEFAULT_REGISTRY is EMPTY: no model is validated for trading; every live candidate abstains (no_validated_model). 'perfect-trader' endpoints retired (410 Gone). | atlas-ml-2: see NC-21 (meta-label pipeline; no eligible model on real data).</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Platt (calibration/__init__, PlattCalibrator) and empirical-bin calibration wired into predict() (commit 47619d5); Brier/log-loss/reliability in research/setup_evidence.py. Isotonic only inside models/quant. Forecast fans: UDF projected rows only. Real-data calibration did not beat base rate for most configs (docs/spec/evidence/price-action-setups-2026-10-23.md).</t>
+          <t>Platt (calibration/__init__, PlattCalibrator) and empirical-bin calibration wired into predict() (commit 47619d5); Brier/log-loss/reliability in research/setup_evidence.py. Isotonic only inside models/quant. Forecast fans: UDF projected rows only. Real-data calibration did not beat base rate for most configs (docs/spec/evidence/price-action-setups-2026-10-23.md). | atlas-ml-2: see NC-21 (meta-label pipeline; no eligible model on real data).</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Purged/embargoed walk-forward, CPCV, PBO (CSCV), DSR in models/quant; experiments/ is a 26-line re-export. Used for the 2026-10-23 real-data evidence (scripts/run_setup_evidence.py). Two registries exist (experiments/ and models/quant/registry) - duplication noted in audit-and-gap.</t>
+          <t>Purged/embargoed walk-forward, CPCV, PBO (CSCV), DSR in models/quant; experiments/ is a 26-line re-export. Used for the 2026-10-23 real-data evidence (scripts/run_setup_evidence.py). Two registries exist (experiments/ and models/quant/registry) - duplication noted in audit-and-gap. | atlas-ml-2: see NC-21 (meta-label pipeline; no eligible model on real data).</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" s="7">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>NC-20</t>
@@ -3318,6 +3318,63 @@
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>NC-21</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Feed-only Meta-Labeling ML Pipeline (triple barrier, purged WF, calibration, conformal abstention, registry, drift, BM25 citations)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>src/atlas/ml/; scripts/ml_refresh.py; scripts/ml_model_card.py; src/atlas/api/ml.py (/api/ml); frontend/src/ui/pages/MlModels.tsx</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>PIT dataset from authoritative feed; setup library as primary model, HGB/logit meta-labeler (take/skip + 1/4-Kelly size); triple-barrier 1-day vertical; venue costs (Binance 24bp RT, US equity 4bp+1c/sh); purged+embargoed (1d) walk-forward; isotonic/Platt; split conformal alpha 0.2 singleton-take; Brier/ECE/AUC/net R/DSR/PBO; versioned registry var/ml/registry (data hash, features, code sha, gates); eligible only if all pre-declared gates pass; PSI + ADWIN drift; forward-only shadow to ShadowCollector; BM25 retrieval over docs/evidence/model cards.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Open-Market + Prop (paper)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>In progress (branch atlas-ml-2)</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>tests/ml/test_ml_pipeline.py: causality, purge/embargo, determinism, gating+load_eligible, calibrator horizon, conformal coverage, PSI/ADWIN, BM25, forward-only shadow, read-only API</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Branch atlas-ml-2 (not merged). Real run 2026-10-23, 8,962 setups (BTC/ETH Binance, SPY/QQQ/IWM; 15m+1h). OOS primary hgb_conformal: crypto-15m brier skill -0.0164 AUC 0.536, 10 taken mean -0.798R; crypto-1h -0.0231/0.517, 134 taken -0.052R; equity-15m -0.284/0.364 (n=93); equity-1h -0.0092/0.525, 28 taken -0.296R. DSR 0 in all groups; PBO 0.198/0.0/n.a./0.036. All 4 groups NOT ELIGIBLE (brier, logloss, DSR, shadow_weeks fail). tests/ml 14 passed. docs/ml/model-card.md.</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
@@ -6707,7 +6764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -10537,12 +10594,12 @@
           <t>NC-16</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C167" s="0" t="inlineStr">
         <is>
           <t>row updated</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E167" s="0" t="inlineStr">
         <is>
           <t>Hub IA: 11 destinations + Advanced, tabs, redirects (branch atlas-ux-3)</t>
         </is>
@@ -10559,14 +10616,58 @@
           <t>Curtain Navigation</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C168" s="0" t="inlineStr">
         <is>
           <t>row updated</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="E168" s="0" t="inlineStr">
         <is>
           <t>Implemented+tested (branch atlas-ux-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Platform Roadmap (A-Z)</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>NC-21</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>row added</t>
+        </is>
+      </c>
+      <c r="E169" s="0" t="inlineStr">
+        <is>
+          <t>In progress (branch atlas-ml-2): meta-label ML pipeline; real OOS fails gates, 0 eligible</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Platform Roadmap (A-Z)</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>M / P / Q</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>notes updated</t>
+        </is>
+      </c>
+      <c r="E170" s="0" t="inlineStr">
+        <is>
+          <t>Cross-reference to NC-21</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -915,7 +915,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>warehouse/__init__.py is a 50-line PIT filter (available_at &lt;= as_of) with a report model. DuckDB is used in features/feature_store.py and api/udf.py. BigQuery, Parquet ZSTD lakehouse, ClickHouse and Databento/Polygon nodes are not wired (named in strings only). Test: tests/test_institutional_expansion.py. | Merged on main (2026-10-23): src/atlas/feeds is the authoritative PIT bar store; udf_feed_bars() (UDF charts + price-action detectors) reads it, falling back to the labelled legacy projection when no series is stored. Yahoo 1h: synthetic 16:00 zero-volume bar dropped, :30-offset bars normalised forward or flagged off_grid_bar (abstain). Tests: tests/feeds, tests/test_udf_spec_parity.py. BigQuery/Parquet/ClickHouse still not wired.</t>
+          <t>warehouse/__init__.py is a 50-line PIT filter (available_at &lt;= as_of) with a report model. DuckDB is used in features/feature_store.py and api/udf.py. BigQuery, Parquet ZSTD lakehouse, ClickHouse and Databento/Polygon nodes are not wired (named in strings only). Test: tests/test_institutional_expansion.py. | Merged on main (2026-10-23): src/atlas/feeds is the authoritative PIT bar store; udf_feed_bars() (UDF charts + price-action detectors) reads it, falling back to the labelled legacy projection when no series is stored. Yahoo 1h: synthetic 16:00 zero-volume bar dropped, :30-offset bars normalised forward or flagged off_grid_bar (abstain). Tests: tests/feeds, tests/test_udf_spec_parity.py. BigQuery/Parquet/ClickHouse still not wired. | atlas-data-2 (2026-10-23): every UI quote now comes from the ATLAS feed (218-symbol UI universe: 43 ETFs, ~123 stocks, 34 crypto, 18 CME futures) with source, Toronto time and status (live/delayed/market_closed/stale/no_data). Live ingest (scripts/run_live_ingest.py): Binance kline WS + Coinbase/Kraken ticker WS + Yahoo spark polling -&gt; last_quotes; /api/feeds/quotes, /api/feeds/health, /api/feeds/stream (SSE). Hardcoded/fixture prices removed. Feed health panel in Settings &gt; Connectors. tests/feeds/test_live_quotes.py.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Verified on main 2026-10-23: src/atlas/feeds + tests/feeds; docs/data-feeds.md. Keyed adapters (Polygon/Databento/Alpaca/Tiingo) are fixture-tested only; no keys configured on this box.</t>
+          <t>Verified on main 2026-10-23: src/atlas/feeds + tests/feeds; docs/data-feeds.md. Keyed adapters (Polygon/Databento/Alpaca/Tiingo) are fixture-tested only; no keys configured on this box. | atlas-data-2 (2026-10-23): every UI quote now comes from the ATLAS feed (218-symbol UI universe: 43 ETFs, ~123 stocks, 34 crypto, 18 CME futures) with source, Toronto time and status (live/delayed/market_closed/stale/no_data). Live ingest (scripts/run_live_ingest.py): Binance kline WS + Coinbase/Kraken ticker WS + Yahoo spark polling -&gt; last_quotes; /api/feeds/quotes, /api/feeds/health, /api/feeds/stream (SSE). Hardcoded/fixture prices removed. Feed health panel in Settings &gt; Connectors. tests/feeds/test_live_quotes.py.</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Desk chart reads the ATLAS feed via udf_feed_bars() (legacy projection fallback, labelled). TradingView widgets + Lightweight Charts merged from atlas-tv-1 (2026-10-23). Databento/Polygon not configured.</t>
+          <t>Desk chart reads the ATLAS feed via udf_feed_bars() (legacy projection fallback, labelled). TradingView widgets + Lightweight Charts merged from atlas-tv-1 (2026-10-23). Databento/Polygon not configured. | atlas-data-2 (2026-10-23): every UI quote now comes from the ATLAS feed (218-symbol UI universe: 43 ETFs, ~123 stocks, 34 crypto, 18 CME futures) with source, Toronto time and status (live/delayed/market_closed/stale/no_data). Live ingest (scripts/run_live_ingest.py): Binance kline WS + Coinbase/Kraken ticker WS + Yahoo spark polling -&gt; last_quotes; /api/feeds/quotes, /api/feeds/health, /api/feeds/stream (SSE). Hardcoded/fixture prices removed. Feed health panel in Settings &gt; Connectors. tests/feeds/test_live_quotes.py.</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -10537,12 +10537,12 @@
           <t>NC-16</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C167" s="0" t="inlineStr">
         <is>
           <t>row updated</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E167" s="0" t="inlineStr">
         <is>
           <t>Hub IA: 11 destinations + Advanced, tabs, redirects (branch atlas-ux-3)</t>
         </is>
@@ -10559,14 +10559,80 @@
           <t>Curtain Navigation</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C168" s="0" t="inlineStr">
         <is>
           <t>row updated</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="E168" s="0" t="inlineStr">
         <is>
           <t>Implemented+tested (branch atlas-ux-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" s="7">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Platform Roadmap (A-Z)</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Data (row 5)</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>row updated</t>
+        </is>
+      </c>
+      <c r="E169" s="0" t="inlineStr">
+        <is>
+          <t>Live quotes from the ATLAS feed with source/status/Toronto time; live ingest + SSE + feed health (branch atlas-data-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" s="7">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Track Rules &amp; Limits</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Data Feeds</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>row updated</t>
+        </is>
+      </c>
+      <c r="E170" s="0" t="inlineStr">
+        <is>
+          <t>Live ingest (Binance/Coinbase/Kraken WS, Yahoo poll); market_closed vs stale vs no_data classification (branch atlas-data-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" s="7">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>14 Workbench Layers &amp; APIs</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Desk / listings</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>row updated</t>
+        </is>
+      </c>
+      <c r="E171" s="0" t="inlineStr">
+        <is>
+          <t>Desk, listings, ticker tape, trade list: no hardcoded or fixture prices; every quote shows source + status (branch atlas-data-2)</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -3377,6 +3377,63 @@
       <c r="K48" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NC-22</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Price-Level Suite, SFP, Gold Opening Box, Strategy Registry &amp; Selector</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>src/atlas/features/price_action/{calendar,contracts,levels,htf,reentry,suite,strategies}.py; src/atlas/ml/selector.py; src/atlas/api/quant.py; frontend LevelsView.tsx (branch atlas-sfp-1)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Causal level registry with available_ts; shared interaction engine; SFP + gold (GC/MGC) ORB/snapback; HTF bias; continuation/reversal/abstain resolve; registry toggles; selector = context + per-family calibrated meta-labels -&gt; EV-ranked pick or NO_TRADE; execution_permission none</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Open-Market + Prop (paper)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>In progress (branch atlas-sfp-1)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>tests/test_level_suite.py (calendar DST/holiday, causality, interaction, box alignment, missing data, parity, resolve, re-entry, HTF, registry/API, cost gate)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Research 2026-10-24: no technique or selector beats NO_TRADE (docs/research/levels-2026-10-24.md); 08:20 box not buildable on 15m; no order flow / econ calendar</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -10734,6 +10791,50 @@
       <c r="E173" s="0" t="inlineStr">
         <is>
           <t>Cross-reference to NC-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Platform Roadmap (A-Z)</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>NC-22</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>row added</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>In progress (branch atlas-sfp-1): price-level suite, SFP, gold box, strategy registry + selector; honest negative research result</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>14 Workbench Layers &amp; APIs</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Research → Levels &amp; sweeps</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>New tab on branch atlas-sfp-1: /api/quant/levels, /api/quant/strategies</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -3381,57 +3381,57 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>NC-22</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>Price-Level Suite, SFP, Gold Opening Box, Strategy Registry &amp; Selector</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>src/atlas/features/price_action/{calendar,contracts,levels,htf,reentry,suite,strategies}.py; src/atlas/ml/selector.py; src/atlas/api/quant.py; frontend LevelsView.tsx (branch atlas-sfp-1)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>Causal level registry with available_ts; shared interaction engine; SFP + gold (GC/MGC) ORB/snapback; HTF bias; continuation/reversal/abstain resolve; registry toggles; selector = context + per-family calibrated meta-labels -&gt; EV-ranked pick or NO_TRADE; execution_permission none</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>Open-Market + Prop (paper)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="0" t="inlineStr">
         <is>
           <t>In progress (branch atlas-sfp-1)</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="0" t="inlineStr">
         <is>
           <t>tests/test_level_suite.py (calendar DST/holiday, causality, interaction, box alignment, missing data, parity, resolve, re-entry, HTF, registry/API, cost gate)</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="0" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="0" t="inlineStr">
         <is>
           <t>Research 2026-10-24: no technique or selector beats NO_TRADE (docs/research/levels-2026-10-24.md); 08:20 box not buildable on 15m; no order flow / econ calendar</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="0" t="inlineStr">
         <is>
           <t>(new)</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
@@ -6821,7 +6821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:F176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -10795,46 +10795,63 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="0" t="inlineStr">
         <is>
           <t>Platform Roadmap (A-Z)</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B174" s="0" t="inlineStr">
         <is>
           <t>NC-22</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C174" s="0" t="inlineStr">
         <is>
           <t>row added</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E174" s="0" t="inlineStr">
         <is>
           <t>In progress (branch atlas-sfp-1): price-level suite, SFP, gold box, strategy registry + selector; honest negative research result</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="0" t="inlineStr">
         <is>
           <t>14 Workbench Layers &amp; APIs</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B175" s="0" t="inlineStr">
         <is>
           <t>Research → Levels &amp; sweeps</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C175" s="0" t="inlineStr">
         <is>
           <t>noted</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="E175" s="0" t="inlineStr">
         <is>
           <t>New tab on branch atlas-sfp-1: /api/quant/levels, /api/quant/strategies</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>atlas-full-1 (unmerged)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Price-action overlays on /api/quant/levels (SMA50/200, trend band, Donchian, BOS/CHoCH, gold-only session ranges from feed 1m with documented gap tolerance + coverage); freshness labels live/delayed/historical/simulated/unavailable; x-correlation-id middleware + JSON request logs. Not done: zone/instrument contract, ML registry merge, replay fills/latency, E2E journey, curtain-menu merge.</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -6821,7 +6821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -10839,19 +10839,36 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B176" s="0" t="inlineStr">
         <is>
           <t>atlas-full-1 (unmerged)</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C176" s="0" t="inlineStr">
         <is>
           <t>Price-action overlays on /api/quant/levels (SMA50/200, trend band, Donchian, BOS/CHoCH, gold-only session ranges from feed 1m with documented gap tolerance + coverage); freshness labels live/delayed/historical/simulated/unavailable; x-correlation-id middleware + JSON request logs. Not done: zone/instrument contract, ML registry merge, replay fills/latency, E2E journey, curtain-menu merge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>atlas-full-1 pass 3 (unmerged)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Unified serving path (6 statuses, drift guard, catalog); correlation id in control-plane/paper/audit records; E2E GC replay journey (0 authorized paper trades: rulebook rejects tight stops / GC contract too large for cap); futures contract specs + multiplier sizing; zone evidence fields, round levels, confluence; replay latency/trade-through/partial fills (1-bar latency turns GC SFP mean R from +0.14 to -0.50); platform-wide freshness chip. Not done: MA/VWAP zone types, curtain section restructuring, asset-card redesign.</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -6821,7 +6821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F177"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -10856,19 +10856,36 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B177" s="0" t="inlineStr">
         <is>
           <t>atlas-full-1 pass 3 (unmerged)</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C177" s="0" t="inlineStr">
         <is>
           <t>Unified serving path (6 statuses, drift guard, catalog); correlation id in control-plane/paper/audit records; E2E GC replay journey (0 authorized paper trades: rulebook rejects tight stops / GC contract too large for cap); futures contract specs + multiplier sizing; zone evidence fields, round levels, confluence; replay latency/trade-through/partial fills (1-bar latency turns GC SFP mean R from +0.14 to -0.50); platform-wide freshness chip. Not done: MA/VWAP zone types, curtain section restructuring, asset-card redesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>atlas-full-1 pass 4</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Futures sizing tests + whole-contract qty fix; EMA/VWAP zones; vertical-text check covers 120 combos; curtain 4 sections; card freshness; MGC eval (0/6 pass, no rule change)</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -6821,7 +6821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -10873,19 +10873,36 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B178" s="0" t="inlineStr">
         <is>
           <t>atlas-full-1 pass 4</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C178" s="0" t="inlineStr">
         <is>
           <t>Futures sizing tests + whole-contract qty fix; EMA/VWAP zones; vertical-text check covers 120 combos; curtain 4 sections; card freshness; MGC eval (0/6 pass, no rule change)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>atlas-full-2 pass 5</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>atlas.intel: lab (DSR/PBO/bootstrap/cost), causal regimes, portfolio VaR/CVaR/stress, track probes, evidence-ID assistant (LLM off), memory/attribution, microstructure gating, Four-Box; exchange_calendars holidays; /research/lab UI</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -3434,6 +3434,33 @@
       <c r="K49" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NC-24</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Model Evolution, Alt Bar Types &amp; Chart Opportunity Markers</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>src/atlas/ml/evolution.py; src/atlas/features/representations/*; src/atlas/intel/markers.py; frontend opportunityMarkers.tsx (branch atlas-evo-1)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Champion/challenger on shared purged WF folds; fitness = EV after costs + BSS + stability; lineage in ML registry; causal markers on confirmation bar; execution_permission none; no model beats baseline on current data</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Open-Market + Prop (paper)</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F179"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -10890,19 +10917,36 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B179" s="0" t="inlineStr">
         <is>
           <t>atlas-full-2 pass 5</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C179" s="0" t="inlineStr">
         <is>
           <t>atlas.intel: lab (DSR/PBO/bootstrap/cost), causal regimes, portfolio VaR/CVaR/stress, track probes, evidence-ID assistant (LLM off), memory/attribution, microstructure gating, Four-Box; exchange_calendars holidays; /research/lab UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>atlas-evo-1 pass 6</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Governed model evolution (bar type as gene, purged WF, no auto-promotion; run d6a35224ceef: no model beats baseline), alt bars (HA/Renko/range/volume/dollar; tick gated), chart opportunity markers + display bar switch, gold zero-trade diagnostics, weekend freshness fix, memory merge</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -3438,29 +3438,86 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>NC-24</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>Model Evolution, Alt Bar Types &amp; Chart Opportunity Markers</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>src/atlas/ml/evolution.py; src/atlas/features/representations/*; src/atlas/intel/markers.py; frontend opportunityMarkers.tsx (branch atlas-evo-1)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>Champion/challenger on shared purged WF folds; fitness = EV after costs + BSS + stability; lineage in ML registry; causal markers on confirmation bar; execution_permission none; no model beats baseline on current data</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>Open-Market + Prop (paper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NC-25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Route Consolidation (one canonical page per function, permanent redirects)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>frontend/src/components/shell/pagesMap.ts (legacyRedirects, tabAliases); frontend/next.config.ts; frontend/app/{control,research,research/lab}/page.tsx; frontend/src/ui/PnlTiles.tsx</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>13 canonical hubs; every former address is a 308 generated from the one registry; retired tabs redirect with explicit ?tab=; no stub page files; nothing removed, only moved</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Open-Market + Prop (paper)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>In progress (branch atlas-routes-1)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>frontend/scripts/pages.test.mjs (5 tests); curl -I 43/43 redirects 308 to canonical; 36 canonical URLs 200; vertical-text 144/144 clean</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>docs/audit/2026-10-24-route-consolidation.md</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F180"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -10934,19 +10991,36 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B180" s="0" t="inlineStr">
         <is>
           <t>atlas-evo-1 pass 6</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C180" s="0" t="inlineStr">
         <is>
           <t>Governed model evolution (bar type as gene, purged WF, no auto-promotion; run d6a35224ceef: no model beats baseline), alt bars (HA/Renko/range/volume/dollar; tick gated), chart opportunity markers + display bar switch, gold zero-trade diagnostics, weekend freshness fix, memory merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>atlas-routes-1 pass 7</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Route consolidation: Risk Positions tab merged into Account &amp; positions; Lab Microstructure -&gt; Research Chart read; Lab Four-Box -&gt; Research Price zones; shared PnL tiles (Overview + Money). 40 stub redirect pages replaced by registry-generated next.config 308 redirects (+3 retired-tab redirects). docs/audit/2026-10-24-route-consolidation.md</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -3465,59 +3465,91 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>NC-25</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>Route Consolidation (one canonical page per function, permanent redirects)</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>frontend/src/components/shell/pagesMap.ts (legacyRedirects, tabAliases); frontend/next.config.ts; frontend/app/{control,research,research/lab}/page.tsx; frontend/src/ui/PnlTiles.tsx</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>13 canonical hubs; every former address is a 308 generated from the one registry; retired tabs redirect with explicit ?tab=; no stub page files; nothing removed, only moved</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>Open-Market + Prop (paper)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="0" t="inlineStr">
         <is>
           <t>In progress (branch atlas-routes-1)</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="0" t="inlineStr">
         <is>
           <t>frontend/scripts/pages.test.mjs (5 tests); curl -I 43/43 redirects 308 to canonical; 36 canonical URLs 200; vertical-text 144/144 clean</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="0" t="inlineStr">
         <is>
           <t>docs/audit/2026-10-24-route-consolidation.md</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="0" t="inlineStr">
         <is>
           <t>(new)</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NC-26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kagi &amp; Point-and-Figure bar representations + accurate marker categories</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>src/atlas/features/representations/builders.py; src/atlas/ml/evolution.py; src/atlas/intel/markers.py; frontend/src/components/market/opportunityMarkers.tsx</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Only completed Kagi lines / P&amp;F columns emitted at completion time; prefix-invariance tested; legend counts per class with n/a when not applicable</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Open-Market + Prop (paper)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>In progress (branch atlas-evo-2)</t>
         </is>
       </c>
     </row>
@@ -6905,7 +6937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -11008,19 +11040,36 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" s="0" t="inlineStr">
         <is>
           <t>atlas-routes-1 pass 7</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C181" s="0" t="inlineStr">
         <is>
           <t>Route consolidation: Risk Positions tab merged into Account &amp; positions; Lab Microstructure -&gt; Research Chart read; Lab Four-Box -&gt; Research Price zones; shared PnL tiles (Overview + Money). 40 stub redirect pages replaced by registry-generated next.config 308 redirects (+3 retired-tab redirects). docs/audit/2026-10-24-route-consolidation.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>atlas-evo-2 pass 8</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Kagi + Point &amp; Figure bars (causal; genes; chart switcher); marker categories accurate (rule-only is not a rejection, n/a classes); evolution run 3bdaaf38ba24: no model beats baseline; dead workspace pathname map removed.</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -3522,34 +3522,91 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>NC-26</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>Kagi &amp; Point-and-Figure bar representations + accurate marker categories</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>src/atlas/features/representations/builders.py; src/atlas/ml/evolution.py; src/atlas/intel/markers.py; frontend/src/components/market/opportunityMarkers.tsx</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>Only completed Kagi lines / P&amp;F columns emitted at completion time; prefix-invariance tested; legend counts per class with n/a when not applicable</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="0" t="inlineStr">
         <is>
           <t>Open-Market + Prop (paper)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="0" t="inlineStr">
         <is>
           <t>In progress (branch atlas-evo-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NC-27</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Re-entry loss caps, one contract source, paper fill realism</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>src/atlas/features/price_action/reentry.py; config/risk_overlays/reentry_tighten.yaml; src/atlas/feeds/contracts.py; src/atlas/features/price_action/replay.py; src/atlas/autopilot/setups.py; src/atlas/execution/paper/broker.py</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Tighten-only loss caps fed by realized paper outcomes; GC/MGC/SI/ES specs from one source (unverified flags kept); latency/trade-through/participation default in PA replay callers</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Open-Market + Prop (paper)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>In progress (branch atlas-evo-3)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>tests/founder/test_evo3_controls.py; tests/autopilot_setups/test_setup_autopilot.py</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>docs/audit/2026-10-24-mandate-checkpoint.md (pass 9)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -11057,19 +11114,36 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B182" s="0" t="inlineStr">
         <is>
           <t>atlas-evo-2 pass 8</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C182" s="0" t="inlineStr">
         <is>
           <t>Kagi + Point &amp; Figure bars (causal; genes; chart switcher); marker categories accurate (rule-only is not a rejection, n/a classes); evolution run 3bdaaf38ba24: no model beats baseline; dead workspace pathname map removed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>atlas-evo-3 pass 9</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>§13 tighten-only re-entry loss caps with causal outcome feedback; §6 single contract-spec source; §25 paper realism default; evolution re-run acfd9abb65cc: no challenger beats baseline</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -3554,57 +3554,114 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>NC-27</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>Re-entry loss caps, one contract source, paper fill realism</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>src/atlas/features/price_action/reentry.py; config/risk_overlays/reentry_tighten.yaml; src/atlas/feeds/contracts.py; src/atlas/features/price_action/replay.py; src/atlas/autopilot/setups.py; src/atlas/execution/paper/broker.py</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>Tighten-only loss caps fed by realized paper outcomes; GC/MGC/SI/ES specs from one source (unverified flags kept); latency/trade-through/participation default in PA replay callers</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>Open-Market + Prop (paper)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="0" t="inlineStr">
         <is>
           <t>In progress (branch atlas-evo-3)</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="0" t="inlineStr">
         <is>
           <t>tests/founder/test_evo3_controls.py; tests/autopilot_setups/test_setup_autopilot.py</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="0" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="0" t="inlineStr">
         <is>
           <t>docs/audit/2026-10-24-mandate-checkpoint.md (pass 9)</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="0" t="inlineStr">
         <is>
           <t>(new)</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NC-28</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Reduce-only partial close, real partial-fill booking, backtester paper realism</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>src/atlas/control/engine.py; src/atlas/autopilot/setups.py; src/atlas/research/backtester.py; src/atlas/strategies/snapback.py; src/atlas/feeds/universe.py; src/atlas/feeds/instruments.py</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>close_position(fraction) reduce-only and audited; autopilot cancels unfilled remainder at zero P&amp;L; StrategyBacktester defaults to PAPER_REALISM; snapback detector runnable; contract terms single source</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Open-Market + Prop (paper)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>In progress (branch atlas-evo-4)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>tests/founder/test_partial_close.py; tests/research/test_backtester_realism.py; tests/autopilot_setups/test_setup_autopilot.py</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>docs/audit/2026-10-24-mandate-checkpoint.md (pass 10)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
@@ -6994,7 +7051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -11131,19 +11188,36 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" s="0" t="inlineStr">
         <is>
           <t>atlas-evo-3 pass 9</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C183" s="0" t="inlineStr">
         <is>
           <t>§13 tighten-only re-entry loss caps with causal outcome feedback; §6 single contract-spec source; §25 paper realism default; evolution re-run acfd9abb65cc: no challenger beats baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>atlas-evo-4 pass 10</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Control-plane reduce-only partial close; autopilot books real partial quantities; backtester paper realism default (before/after on real bars, little change on liquid markets); snapback detector fixed; contract terms deduplicated; ML not re-run (labels unchanged)</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -3611,59 +3611,101 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>NC-28</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>Reduce-only partial close, real partial-fill booking, backtester paper realism</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>src/atlas/control/engine.py; src/atlas/autopilot/setups.py; src/atlas/research/backtester.py; src/atlas/strategies/snapback.py; src/atlas/feeds/universe.py; src/atlas/feeds/instruments.py</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>close_position(fraction) reduce-only and audited; autopilot cancels unfilled remainder at zero P&amp;L; StrategyBacktester defaults to PAPER_REALISM; snapback detector runnable; contract terms single source</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr">
         <is>
           <t>Open-Market + Prop (paper)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="0" t="inlineStr">
         <is>
           <t>In progress (branch atlas-evo-4)</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="0" t="inlineStr">
         <is>
           <t>tests/founder/test_partial_close.py; tests/research/test_backtester_realism.py; tests/autopilot_setups/test_setup_autopilot.py</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="0" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="0" t="inlineStr">
         <is>
           <t>docs/audit/2026-10-24-mandate-checkpoint.md (pass 10)</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="0" t="inlineStr">
         <is>
           <t>(new)</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K54" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>NC-29</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>Section 22 macro data (keyless FRED, release-lagged) + HTF context gene + ML diagnosis</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>src/atlas/feeds/providers/fred_public.py; scripts/fetch_fred_public.py; src/atlas/ml/context.py; src/atlas/ml/evolution.py; scripts/evolve_models.py; scripts/ml_diagnose.py; docs/ml/evo5-diagnosis.md</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>DGS10/DGS2/VIXCLS/DTWEXBGS/CPIAUCNS in feed observations with conservative availability dates; context gene none|htf|macro|htf_macro; extended universe option; runs 44f40efd9e65 and 30721a3ccb32: no challenger beats baseline (primary setups have negative gross R)</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>Open-Market + Prop (paper)</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>In progress (branch atlas-evo-5)</t>
+        </is>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>tests/test_macro_context.py; tests/test_evolution.py</t>
+        </is>
+      </c>
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -11205,19 +11247,36 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B184" s="0" t="inlineStr">
         <is>
           <t>atlas-evo-4 pass 10</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C184" s="0" t="inlineStr">
         <is>
           <t>Control-plane reduce-only partial close; autopilot books real partial quantities; backtester paper realism default (before/after on real bars, little change on liquid markets); snapback detector fixed; contract terms deduplicated; ML not re-run (labels unchanged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
+          <t>atlas-evo-5 pass 11</t>
+        </is>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t>Section 22 macro via keyless FRED with release lags (no lookahead tests); HTF + macro context gene; extended 15m+1h universe; ML diagnosis (negative gross edge, costs ~0.5 R, AUC ~0.53, no leakage); evolution runs 44f40efd9e65 / 30721a3ccb32 no challenger beats baseline; nothing promoted</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -3611,59 +3611,101 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>NC-28</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>Reduce-only partial close, real partial-fill booking, backtester paper realism</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>src/atlas/control/engine.py; src/atlas/autopilot/setups.py; src/atlas/research/backtester.py; src/atlas/strategies/snapback.py; src/atlas/feeds/universe.py; src/atlas/feeds/instruments.py</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>close_position(fraction) reduce-only and audited; autopilot cancels unfilled remainder at zero P&amp;L; StrategyBacktester defaults to PAPER_REALISM; snapback detector runnable; contract terms single source</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr">
         <is>
           <t>Open-Market + Prop (paper)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="0" t="inlineStr">
         <is>
           <t>In progress (branch atlas-evo-4)</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="0" t="inlineStr">
         <is>
           <t>tests/founder/test_partial_close.py; tests/research/test_backtester_realism.py; tests/autopilot_setups/test_setup_autopilot.py</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="0" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="0" t="inlineStr">
         <is>
           <t>docs/audit/2026-10-24-mandate-checkpoint.md (pass 10)</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="0" t="inlineStr">
         <is>
           <t>(new)</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K54" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>X (ext-1)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Seven-repo extensions</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>src/atlas/ext/, /api/ext/*</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Options/VaR/DCF/EDGAR/scan/Pine/dossier/personas/agent pipeline/Alpaca paper/alerts/MCP (read-only). Research/paper only.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>All tracks (research)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Built on atlas-ext-1 (unmerged)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>tests/ext/test_ext.py (20 tests)</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -11205,19 +11247,31 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B184" s="0" t="inlineStr">
         <is>
           <t>atlas-evo-4 pass 10</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C184" s="0" t="inlineStr">
         <is>
           <t>Control-plane reduce-only partial close; autopilot books real partial quantities; backtester paper realism default (before/after on real bars, little change on liquid markets); snapback detector fixed; contract terms deduplicated; ML not re-run (labels unchanged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>atlas-ext-1: seven-repo gap audit + atlas.ext modules; blocked: option chains, news, maritime; yield curve deferred to evo-5</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -3710,42 +3710,42 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>X (ext-1)</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>Seven-repo extensions</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>src/atlas/ext/, /api/ext/*</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>Options/VaR/DCF/EDGAR/scan/Pine/dossier/personas/agent pipeline/Alpaca paper/alerts/MCP (read-only). Research/paper only.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="0" t="inlineStr">
         <is>
           <t>All tracks (research)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="0" t="inlineStr">
         <is>
           <t>Built on atlas-ext-1</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="0" t="inlineStr">
         <is>
           <t>tests/ext/test_ext.py (20 tests)</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="0" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -7135,7 +7135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -11323,14 +11323,31 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B186" s="0" t="inlineStr">
         <is>
           <t>atlas-ext-1: seven-repo gap audit + atlas.ext modules; blocked: option chains, news, maritime; yield curve owned by evo-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>atlas-evo-6 pass 12</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Setup redesign research: ATR stops / R targets / cost filter variants on 15m/1h/4h (paper realism, purged WF, DSR, PBO, bootstrap); 0/230 pass gates; only PDR 4h crypto gross-positive (CI spans 0); orb_retest 15m research-retired (reversible); evolution de86779da75c / f8e7de55c108 no challenger beats baseline; nothing promoted</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -3748,6 +3748,48 @@
       <c r="H56" s="0" t="inlineStr">
         <is>
           <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>U (unify-1)</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>AI as one node + repo streamline</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>src/atlas/ai/node.py; src/atlas/ai/http.py; /api/ai/*; docs/architecture/AI_NODE.md</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>One registry/status/audit; execution_permission none enforced at one middleware for all AI paths; dead code, unused deps removed; broken scripts fixed</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>All tracks (research)</t>
+        </is>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>Implemented+tested</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>tests/test_ai_node.py</t>
+        </is>
+      </c>
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="7" min="1" max="1"/>
@@ -11335,19 +11377,36 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B187" s="0" t="inlineStr">
         <is>
           <t>atlas-evo-6 pass 12</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C187" s="0" t="inlineStr">
         <is>
           <t>Setup redesign research: ATR stops / R targets / cost filter variants on 15m/1h/4h (paper realism, purged WF, DSR, PBO, bootstrap); 0/230 pass gates; only PDR 4h crypto gross-positive (CI spans 0); orb_retest 15m research-retired (reversible); evolution de86779da75c / f8e7de55c108 no challenger beats baseline; nothing promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>atlas-unify-1 streamline pass 1</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AI consolidated into one node (atlas.ai, /api/ai/*, single execution_permission none guard); broken scripts fixed; dead modules/artifacts and 5 unused deps removed; one brier</t>
         </is>
       </c>
     </row>

--- a/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
+++ b/ATLAS Platform Master Roadmap & Technical Specifications (A-Z).xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="19.25" customWidth="1" style="7" min="1" max="1"/>
@@ -3790,6 +3790,53 @@
       <c r="H57" s="0" t="inlineStr">
         <is>
           <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>E (evo7)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PDR reversal probe + ML meta-label</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>src/atlas/research/reversal_probe.py; scripts/run_reversal_probe.py; docs/research/evo7-reversal-probe.md; docs/ml/evo7-reversal-probe.md</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Limit/partial/time-stop/closed-bar HTF+vol filters, maker_assumed costs labelled; CIs, DSR, PBO, purged WF over all 540 trials; ML evo7/evo7_1h</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Crypto research (paper)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Implemented+tested (research only)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>tests/test_evo7_probe.py</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0/540 pass, PBO 0.109; 1h ML research champion 432dba69a77e fragile; execution_permission none</t>
         </is>
       </c>
     </row>
@@ -11394,17 +11441,17 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="0" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B188" s="0" t="inlineStr">
         <is>
           <t>atlas-unify-1 streamline pass 1</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
+      <c r="C188" s="0" t="inlineStr">
         <is>
           <t>AI consolidated into one node (atlas.ai, /api/ai/*, single execution_permission none guard); broken scripts fixed; dead modules/artifacts and 5 unused deps removed; one brier</t>
         </is>
